--- a/files/NRL_anytime_tryscorers.xlsx
+++ b/files/NRL_anytime_tryscorers.xlsx
@@ -26,55 +26,52 @@
     <t xml:space="preserve">Price</t>
   </si>
   <si>
-    <t xml:space="preserve">cronulla-sutherland sharks at sydney roosters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cronulla-sutherland sharks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ronaldo Mulitalo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sione Katoa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">William Kennedy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kayal Iro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Braydon Trindall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riley Jones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Briton Nikora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teig Wilton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nicholas Hynes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Addin Fonua-Blake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siosifa Talakai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Hazelton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blayke Brailey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jesse Colquhoun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cameron McInnes</t>
+    <t xml:space="preserve">sydney roosters at dolphins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dolphins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamiso Tabuai-Fidow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selwyn Cobbo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jamayne Isaako</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herbie Farnworth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Bostock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connelly Lemuelu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max Plath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kulikefu Finefeuiaki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kodi Nikorima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeremy Marshall-King</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ray Stone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Flegler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaiya Katoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tom Gilbert</t>
   </si>
   <si>
     <t xml:space="preserve">sydney roosters</t>
@@ -95,37 +92,40 @@
     <t xml:space="preserve">Billy Smith</t>
   </si>
   <si>
+    <t xml:space="preserve">Sam Walker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daly Cherry-Evans</t>
+  </si>
+  <si>
     <t xml:space="preserve">Salesi Foketi</t>
   </si>
   <si>
     <t xml:space="preserve">Siua Wong</t>
   </si>
   <si>
-    <t xml:space="preserve">Daly Cherry-Evans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hugo Savala</t>
-  </si>
-  <si>
     <t xml:space="preserve">Reece Robson</t>
   </si>
   <si>
     <t xml:space="preserve">Victor Radley</t>
   </si>
   <si>
+    <t xml:space="preserve">Connor Watson</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nat Butcher</t>
   </si>
   <si>
-    <t xml:space="preserve">Toby Rodwell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connor Watson</t>
+    <t xml:space="preserve">Lindsay Collins</t>
   </si>
   <si>
     <t xml:space="preserve">Spencer Leniu</t>
   </si>
   <si>
-    <t xml:space="preserve">newcastle knights at warriors</t>
+    <t xml:space="preserve">Egan Butcher</t>
+  </si>
+  <si>
+    <t xml:space="preserve">newcastle knights at penrith panthers</t>
   </si>
   <si>
     <t xml:space="preserve">newcastle knights</t>
@@ -170,58 +170,58 @@
     <t xml:space="preserve">Elijah Salesa-Leaumoana</t>
   </si>
   <si>
-    <t xml:space="preserve">warriors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alofiana Khan-Pereira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charnze Nicoll-Klokstad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ali Leiataua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taine Tuaupiki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurt Capewell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jacob Laban</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chanel Harris-Tavita</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Te Maire Martin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leka Halasima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adam Pompey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wayde Egan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">James Fisher-Harris</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Erin Clark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sam Healey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eddie Ieremia-Toeava</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Demitric Vaimauga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mitchell Barnett</t>
+    <t xml:space="preserve">penrith panthers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas Jenkins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brian To'o</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casey McLean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dylan Edwards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blaize Talagi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaiah Papali'i</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liam Martin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nathan Cleary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Cole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Izack Tago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lindsay Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liam Henry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isaah Yeo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luke Garner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moses Leota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scott Sorensen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mitch Kenny</t>
   </si>
 </sst>
 </file>
@@ -550,8 +550,8 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="45.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="26.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="37.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="17.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="23.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="5.71" hidden="0" customWidth="1"/>
   </cols>
@@ -581,7 +581,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="3">
@@ -595,7 +595,7 @@
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="4">
@@ -609,7 +609,7 @@
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>3.31</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="5">
@@ -623,7 +623,7 @@
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>3.41</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="6">
@@ -637,7 +637,7 @@
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>3.57</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="8">
@@ -665,7 +665,7 @@
         <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>4.46</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="9">
@@ -679,7 +679,7 @@
         <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>4.46</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="10">
@@ -693,7 +693,7 @@
         <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>5.06</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="11">
@@ -707,7 +707,7 @@
         <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>5.95</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="12">
@@ -721,7 +721,7 @@
         <v>16</v>
       </c>
       <c r="D12" t="n">
-        <v>8.64</v>
+        <v>9.04</v>
       </c>
     </row>
     <row r="13">
@@ -735,7 +735,7 @@
         <v>17</v>
       </c>
       <c r="D13" t="n">
-        <v>10.05</v>
+        <v>10.71</v>
       </c>
     </row>
     <row r="14">
@@ -749,7 +749,7 @@
         <v>18</v>
       </c>
       <c r="D14" t="n">
-        <v>10.7</v>
+        <v>11.82</v>
       </c>
     </row>
     <row r="15">
@@ -763,7 +763,7 @@
         <v>19</v>
       </c>
       <c r="D15" t="n">
-        <v>13.51</v>
+        <v>16.19</v>
       </c>
     </row>
     <row r="16">
@@ -771,13 +771,13 @@
         <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D16" t="n">
-        <v>14.36</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="17">
@@ -785,13 +785,13 @@
         <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C17" t="s">
         <v>22</v>
       </c>
       <c r="D17" t="n">
-        <v>1.84</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="18">
@@ -799,13 +799,13 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C18" t="s">
         <v>23</v>
       </c>
       <c r="D18" t="n">
-        <v>2.08</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="19">
@@ -813,13 +813,13 @@
         <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C19" t="s">
         <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>2.6</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="20">
@@ -827,13 +827,13 @@
         <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C20" t="s">
         <v>25</v>
       </c>
       <c r="D20" t="n">
-        <v>3.12</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="21">
@@ -841,13 +841,13 @@
         <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C21" t="s">
         <v>26</v>
       </c>
       <c r="D21" t="n">
-        <v>3.64</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="22">
@@ -855,13 +855,13 @@
         <v>4</v>
       </c>
       <c r="B22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C22" t="s">
         <v>27</v>
       </c>
       <c r="D22" t="n">
-        <v>4.51</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="23">
@@ -869,7 +869,7 @@
         <v>4</v>
       </c>
       <c r="B23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C23" t="s">
         <v>28</v>
@@ -883,13 +883,13 @@
         <v>4</v>
       </c>
       <c r="B24" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C24" t="s">
         <v>29</v>
       </c>
       <c r="D24" t="n">
-        <v>4.54</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="25">
@@ -897,13 +897,13 @@
         <v>4</v>
       </c>
       <c r="B25" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C25" t="s">
         <v>30</v>
       </c>
       <c r="D25" t="n">
-        <v>5.94</v>
+        <v>8.53</v>
       </c>
     </row>
     <row r="26">
@@ -911,13 +911,13 @@
         <v>4</v>
       </c>
       <c r="B26" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C26" t="s">
         <v>31</v>
       </c>
       <c r="D26" t="n">
-        <v>8.45</v>
+        <v>8.84</v>
       </c>
     </row>
     <row r="27">
@@ -925,13 +925,13 @@
         <v>4</v>
       </c>
       <c r="B27" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C27" t="s">
         <v>32</v>
       </c>
       <c r="D27" t="n">
-        <v>8.73</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="28">
@@ -939,13 +939,13 @@
         <v>4</v>
       </c>
       <c r="B28" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C28" t="s">
         <v>33</v>
       </c>
       <c r="D28" t="n">
-        <v>11.15</v>
+        <v>11.41</v>
       </c>
     </row>
     <row r="29">
@@ -953,13 +953,13 @@
         <v>4</v>
       </c>
       <c r="B29" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C29" t="s">
         <v>34</v>
       </c>
       <c r="D29" t="n">
-        <v>11.21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30">
@@ -967,13 +967,13 @@
         <v>4</v>
       </c>
       <c r="B30" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C30" t="s">
         <v>35</v>
       </c>
       <c r="D30" t="n">
-        <v>11.53</v>
+        <v>13.07</v>
       </c>
     </row>
     <row r="31">
@@ -981,13 +981,13 @@
         <v>4</v>
       </c>
       <c r="B31" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C31" t="s">
         <v>36</v>
       </c>
       <c r="D31" t="n">
-        <v>12.91</v>
+        <v>13.69</v>
       </c>
     </row>
     <row r="32">
@@ -1001,7 +1001,7 @@
         <v>39</v>
       </c>
       <c r="D32" t="n">
-        <v>1.93</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="33">
@@ -1015,7 +1015,7 @@
         <v>40</v>
       </c>
       <c r="D33" t="n">
-        <v>2.21</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="34">
@@ -1029,7 +1029,7 @@
         <v>41</v>
       </c>
       <c r="D34" t="n">
-        <v>2.56</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="35">
@@ -1043,7 +1043,7 @@
         <v>42</v>
       </c>
       <c r="D35" t="n">
-        <v>3.32</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="36">
@@ -1057,7 +1057,7 @@
         <v>43</v>
       </c>
       <c r="D36" t="n">
-        <v>3.98</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="37">
@@ -1071,7 +1071,7 @@
         <v>44</v>
       </c>
       <c r="D37" t="n">
-        <v>4.32</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="38">
@@ -1085,7 +1085,7 @@
         <v>45</v>
       </c>
       <c r="D38" t="n">
-        <v>4.32</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="39">
@@ -1099,7 +1099,7 @@
         <v>46</v>
       </c>
       <c r="D39" t="n">
-        <v>5.06</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="40">
@@ -1113,7 +1113,7 @@
         <v>47</v>
       </c>
       <c r="D40" t="n">
-        <v>6.97</v>
+        <v>8.76</v>
       </c>
     </row>
     <row r="41">
@@ -1127,7 +1127,7 @@
         <v>48</v>
       </c>
       <c r="D41" t="n">
-        <v>9.07</v>
+        <v>11.41</v>
       </c>
     </row>
     <row r="42">
@@ -1141,7 +1141,7 @@
         <v>49</v>
       </c>
       <c r="D42" t="n">
-        <v>9.51</v>
+        <v>12.11</v>
       </c>
     </row>
     <row r="43">
@@ -1155,7 +1155,7 @@
         <v>50</v>
       </c>
       <c r="D43" t="n">
-        <v>10.15</v>
+        <v>13.13</v>
       </c>
     </row>
     <row r="44">
@@ -1169,7 +1169,7 @@
         <v>51</v>
       </c>
       <c r="D44" t="n">
-        <v>15.82</v>
+        <v>19.77</v>
       </c>
     </row>
     <row r="45">
@@ -1183,7 +1183,7 @@
         <v>53</v>
       </c>
       <c r="D45" t="n">
-        <v>1.52</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="46">
@@ -1197,7 +1197,7 @@
         <v>54</v>
       </c>
       <c r="D46" t="n">
-        <v>2.81</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="47">
@@ -1211,7 +1211,7 @@
         <v>55</v>
       </c>
       <c r="D47" t="n">
-        <v>3.01</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="48">
@@ -1225,7 +1225,7 @@
         <v>56</v>
       </c>
       <c r="D48" t="n">
-        <v>3.24</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="49">
@@ -1239,7 +1239,7 @@
         <v>57</v>
       </c>
       <c r="D49" t="n">
-        <v>3.46</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="50">
@@ -1253,7 +1253,7 @@
         <v>58</v>
       </c>
       <c r="D50" t="n">
-        <v>3.46</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="51">
@@ -1267,7 +1267,7 @@
         <v>59</v>
       </c>
       <c r="D51" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="52">
@@ -1281,7 +1281,7 @@
         <v>60</v>
       </c>
       <c r="D52" t="n">
-        <v>3.76</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="53">
@@ -1295,7 +1295,7 @@
         <v>61</v>
       </c>
       <c r="D53" t="n">
-        <v>3.78</v>
+        <v>6.28</v>
       </c>
     </row>
     <row r="54">
@@ -1309,7 +1309,7 @@
         <v>62</v>
       </c>
       <c r="D54" t="n">
-        <v>3.87</v>
+        <v>8.17</v>
       </c>
     </row>
     <row r="55">
@@ -1323,7 +1323,7 @@
         <v>63</v>
       </c>
       <c r="D55" t="n">
-        <v>5.83</v>
+        <v>8.42</v>
       </c>
     </row>
     <row r="56">
@@ -1337,7 +1337,7 @@
         <v>64</v>
       </c>
       <c r="D56" t="n">
-        <v>8.27</v>
+        <v>9.36</v>
       </c>
     </row>
     <row r="57">
@@ -1351,7 +1351,7 @@
         <v>65</v>
       </c>
       <c r="D57" t="n">
-        <v>8.32</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="58">
@@ -1365,7 +1365,7 @@
         <v>66</v>
       </c>
       <c r="D58" t="n">
-        <v>11.03</v>
+        <v>12.34</v>
       </c>
     </row>
     <row r="59">
@@ -1379,7 +1379,7 @@
         <v>67</v>
       </c>
       <c r="D59" t="n">
-        <v>13.19</v>
+        <v>15.27</v>
       </c>
     </row>
     <row r="60">
@@ -1393,7 +1393,7 @@
         <v>68</v>
       </c>
       <c r="D60" t="n">
-        <v>13.83</v>
+        <v>18.94</v>
       </c>
     </row>
     <row r="61">
@@ -1407,7 +1407,7 @@
         <v>69</v>
       </c>
       <c r="D61" t="n">
-        <v>14.21</v>
+        <v>21.48</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_anytime_tryscorers.xlsx
+++ b/files/NRL_anytime_tryscorers.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t xml:space="preserve">Game</t>
   </si>
@@ -26,52 +26,46 @@
     <t xml:space="preserve">Price</t>
   </si>
   <si>
-    <t xml:space="preserve">sydney roosters at dolphins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dolphins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamiso Tabuai-Fidow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Selwyn Cobbo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jamayne Isaako</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herbie Farnworth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Bostock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connelly Lemuelu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Plath</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kulikefu Finefeuiaki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kodi Nikorima</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeremy Marshall-King</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ray Stone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Flegler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaiya Katoa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tom Gilbert</t>
+    <t xml:space="preserve">newcastle knights at sydney roosters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">newcastle knights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dominic Young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greg Marzhew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fletcher Sharpe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bradman Best</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kalyn Ponga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jermaine McEwen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Francis Manuleleua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dane Gagai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sandon Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fletcher Hunt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harrison Graham</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elijah Salesa-Leaumoana</t>
   </si>
   <si>
     <t xml:space="preserve">sydney roosters</t>
@@ -125,103 +119,10 @@
     <t xml:space="preserve">Egan Butcher</t>
   </si>
   <si>
-    <t xml:space="preserve">newcastle knights at penrith panthers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">newcastle knights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dominic Young</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Greg Marzhew</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fletcher Sharpe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bradman Best</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kalyn Ponga</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jermaine McEwen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Francis Manuleleua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dane Gagai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sandon Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phoenix Crossland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harrison Graham</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fletcher Hunt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elijah Salesa-Leaumoana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">penrith panthers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas Jenkins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brian To'o</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casey McLean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dylan Edwards</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blaize Talagi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaiah Papali'i</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liam Martin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nathan Cleary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Cole</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Izack Tago</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lindsay Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liam Henry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isaah Yeo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luke Garner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Moses Leota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scott Sorensen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mitch Kenny</t>
+    <t xml:space="preserve">Cody Ramsey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angus Crichton</t>
   </si>
 </sst>
 </file>
@@ -550,7 +451,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="37.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="36.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="17.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="23.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="5.71" hidden="0" customWidth="1"/>
@@ -581,7 +482,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>2.12</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="3">
@@ -595,7 +496,7 @@
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>2.13</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="4">
@@ -609,7 +510,7 @@
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>2.35</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="5">
@@ -623,7 +524,7 @@
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>2.61</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="6">
@@ -637,7 +538,7 @@
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>3.43</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +552,7 @@
         <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>4.16</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="8">
@@ -665,7 +566,7 @@
         <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>4.57</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="9">
@@ -679,7 +580,7 @@
         <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>4.57</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="10">
@@ -693,7 +594,7 @@
         <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>5.77</v>
+        <v>7.38</v>
       </c>
     </row>
     <row r="11">
@@ -707,7 +608,7 @@
         <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>7.41</v>
+        <v>11.02</v>
       </c>
     </row>
     <row r="12">
@@ -721,7 +622,7 @@
         <v>16</v>
       </c>
       <c r="D12" t="n">
-        <v>9.04</v>
+        <v>12.83</v>
       </c>
     </row>
     <row r="13">
@@ -735,7 +636,7 @@
         <v>17</v>
       </c>
       <c r="D13" t="n">
-        <v>10.71</v>
+        <v>16.53</v>
       </c>
     </row>
     <row r="14">
@@ -743,13 +644,13 @@
         <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D14" t="n">
-        <v>11.82</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="15">
@@ -757,13 +658,13 @@
         <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D15" t="n">
-        <v>16.19</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="16">
@@ -771,13 +672,13 @@
         <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C16" t="s">
         <v>21</v>
       </c>
       <c r="D16" t="n">
-        <v>1.81</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="17">
@@ -785,13 +686,13 @@
         <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C17" t="s">
         <v>22</v>
       </c>
       <c r="D17" t="n">
-        <v>2.08</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="18">
@@ -799,13 +700,13 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C18" t="s">
         <v>23</v>
       </c>
       <c r="D18" t="n">
-        <v>2.59</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="19">
@@ -813,13 +714,13 @@
         <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C19" t="s">
         <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>3.06</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="20">
@@ -827,13 +728,13 @@
         <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C20" t="s">
         <v>25</v>
       </c>
       <c r="D20" t="n">
-        <v>3.7</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="21">
@@ -841,13 +742,13 @@
         <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="s">
         <v>26</v>
       </c>
       <c r="D21" t="n">
-        <v>4.25</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="22">
@@ -855,13 +756,13 @@
         <v>4</v>
       </c>
       <c r="B22" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C22" t="s">
         <v>27</v>
       </c>
       <c r="D22" t="n">
-        <v>4.47</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="23">
@@ -869,13 +770,13 @@
         <v>4</v>
       </c>
       <c r="B23" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C23" t="s">
         <v>28</v>
       </c>
       <c r="D23" t="n">
-        <v>4.51</v>
+        <v>7.63</v>
       </c>
     </row>
     <row r="24">
@@ -883,13 +784,13 @@
         <v>4</v>
       </c>
       <c r="B24" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C24" t="s">
         <v>29</v>
       </c>
       <c r="D24" t="n">
-        <v>4.51</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="25">
@@ -897,13 +798,13 @@
         <v>4</v>
       </c>
       <c r="B25" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C25" t="s">
         <v>30</v>
       </c>
       <c r="D25" t="n">
-        <v>8.53</v>
+        <v>9.18</v>
       </c>
     </row>
     <row r="26">
@@ -911,13 +812,13 @@
         <v>4</v>
       </c>
       <c r="B26" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C26" t="s">
         <v>31</v>
       </c>
       <c r="D26" t="n">
-        <v>8.84</v>
+        <v>10.19</v>
       </c>
     </row>
     <row r="27">
@@ -925,13 +826,13 @@
         <v>4</v>
       </c>
       <c r="B27" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C27" t="s">
         <v>32</v>
       </c>
       <c r="D27" t="n">
-        <v>10.27</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="28">
@@ -939,13 +840,13 @@
         <v>4</v>
       </c>
       <c r="B28" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C28" t="s">
         <v>33</v>
       </c>
       <c r="D28" t="n">
-        <v>11.41</v>
+        <v>11.67</v>
       </c>
     </row>
     <row r="29">
@@ -953,13 +854,13 @@
         <v>4</v>
       </c>
       <c r="B29" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C29" t="s">
         <v>34</v>
       </c>
       <c r="D29" t="n">
-        <v>13</v>
+        <v>12.21</v>
       </c>
     </row>
     <row r="30">
@@ -967,13 +868,13 @@
         <v>4</v>
       </c>
       <c r="B30" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C30" t="s">
         <v>35</v>
       </c>
       <c r="D30" t="n">
-        <v>13.07</v>
+        <v>15.98</v>
       </c>
     </row>
     <row r="31">
@@ -981,433 +882,13 @@
         <v>4</v>
       </c>
       <c r="B31" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C31" t="s">
         <v>36</v>
       </c>
       <c r="D31" t="n">
-        <v>13.69</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" t="s">
-        <v>38</v>
-      </c>
-      <c r="C32" t="s">
-        <v>39</v>
-      </c>
-      <c r="D32" t="n">
-        <v>2.26</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" t="s">
-        <v>38</v>
-      </c>
-      <c r="C33" t="s">
-        <v>40</v>
-      </c>
-      <c r="D33" t="n">
-        <v>2.64</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" t="s">
-        <v>38</v>
-      </c>
-      <c r="C34" t="s">
-        <v>41</v>
-      </c>
-      <c r="D34" t="n">
-        <v>3.02</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" t="s">
-        <v>38</v>
-      </c>
-      <c r="C35" t="s">
-        <v>42</v>
-      </c>
-      <c r="D35" t="n">
-        <v>4.07</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" t="s">
-        <v>38</v>
-      </c>
-      <c r="C36" t="s">
-        <v>43</v>
-      </c>
-      <c r="D36" t="n">
-        <v>4.92</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" t="s">
-        <v>38</v>
-      </c>
-      <c r="C37" t="s">
-        <v>44</v>
-      </c>
-      <c r="D37" t="n">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>37</v>
-      </c>
-      <c r="B38" t="s">
-        <v>38</v>
-      </c>
-      <c r="C38" t="s">
-        <v>45</v>
-      </c>
-      <c r="D38" t="n">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" t="s">
-        <v>38</v>
-      </c>
-      <c r="C39" t="s">
-        <v>46</v>
-      </c>
-      <c r="D39" t="n">
-        <v>6.27</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>37</v>
-      </c>
-      <c r="B40" t="s">
-        <v>38</v>
-      </c>
-      <c r="C40" t="s">
-        <v>47</v>
-      </c>
-      <c r="D40" t="n">
-        <v>8.76</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>37</v>
-      </c>
-      <c r="B41" t="s">
-        <v>38</v>
-      </c>
-      <c r="C41" t="s">
-        <v>48</v>
-      </c>
-      <c r="D41" t="n">
-        <v>11.41</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" t="s">
-        <v>38</v>
-      </c>
-      <c r="C42" t="s">
-        <v>49</v>
-      </c>
-      <c r="D42" t="n">
-        <v>12.11</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" t="s">
-        <v>38</v>
-      </c>
-      <c r="C43" t="s">
-        <v>50</v>
-      </c>
-      <c r="D43" t="n">
-        <v>13.13</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" t="s">
-        <v>38</v>
-      </c>
-      <c r="C44" t="s">
-        <v>51</v>
-      </c>
-      <c r="D44" t="n">
-        <v>19.77</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>37</v>
-      </c>
-      <c r="B45" t="s">
-        <v>52</v>
-      </c>
-      <c r="C45" t="s">
-        <v>53</v>
-      </c>
-      <c r="D45" t="n">
-        <v>1.82</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>37</v>
-      </c>
-      <c r="B46" t="s">
-        <v>52</v>
-      </c>
-      <c r="C46" t="s">
-        <v>54</v>
-      </c>
-      <c r="D46" t="n">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>37</v>
-      </c>
-      <c r="B47" t="s">
-        <v>52</v>
-      </c>
-      <c r="C47" t="s">
-        <v>55</v>
-      </c>
-      <c r="D47" t="n">
-        <v>2.45</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>37</v>
-      </c>
-      <c r="B48" t="s">
-        <v>52</v>
-      </c>
-      <c r="C48" t="s">
-        <v>56</v>
-      </c>
-      <c r="D48" t="n">
-        <v>2.89</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" t="s">
-        <v>52</v>
-      </c>
-      <c r="C49" t="s">
-        <v>57</v>
-      </c>
-      <c r="D49" t="n">
-        <v>3.74</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>37</v>
-      </c>
-      <c r="B50" t="s">
-        <v>52</v>
-      </c>
-      <c r="C50" t="s">
-        <v>58</v>
-      </c>
-      <c r="D50" t="n">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>37</v>
-      </c>
-      <c r="B51" t="s">
-        <v>52</v>
-      </c>
-      <c r="C51" t="s">
-        <v>59</v>
-      </c>
-      <c r="D51" t="n">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" t="s">
-        <v>52</v>
-      </c>
-      <c r="C52" t="s">
-        <v>60</v>
-      </c>
-      <c r="D52" t="n">
-        <v>4.4</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" t="s">
-        <v>52</v>
-      </c>
-      <c r="C53" t="s">
-        <v>61</v>
-      </c>
-      <c r="D53" t="n">
-        <v>6.28</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>37</v>
-      </c>
-      <c r="B54" t="s">
-        <v>52</v>
-      </c>
-      <c r="C54" t="s">
-        <v>62</v>
-      </c>
-      <c r="D54" t="n">
-        <v>8.17</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>37</v>
-      </c>
-      <c r="B55" t="s">
-        <v>52</v>
-      </c>
-      <c r="C55" t="s">
-        <v>63</v>
-      </c>
-      <c r="D55" t="n">
-        <v>8.42</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>37</v>
-      </c>
-      <c r="B56" t="s">
-        <v>52</v>
-      </c>
-      <c r="C56" t="s">
-        <v>64</v>
-      </c>
-      <c r="D56" t="n">
-        <v>9.36</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>37</v>
-      </c>
-      <c r="B57" t="s">
-        <v>52</v>
-      </c>
-      <c r="C57" t="s">
-        <v>65</v>
-      </c>
-      <c r="D57" t="n">
-        <v>9.48</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>37</v>
-      </c>
-      <c r="B58" t="s">
-        <v>52</v>
-      </c>
-      <c r="C58" t="s">
-        <v>66</v>
-      </c>
-      <c r="D58" t="n">
-        <v>12.34</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s">
-        <v>37</v>
-      </c>
-      <c r="B59" t="s">
-        <v>52</v>
-      </c>
-      <c r="C59" t="s">
-        <v>67</v>
-      </c>
-      <c r="D59" t="n">
-        <v>15.27</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>37</v>
-      </c>
-      <c r="B60" t="s">
-        <v>52</v>
-      </c>
-      <c r="C60" t="s">
-        <v>68</v>
-      </c>
-      <c r="D60" t="n">
-        <v>18.94</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>37</v>
-      </c>
-      <c r="B61" t="s">
-        <v>52</v>
-      </c>
-      <c r="C61" t="s">
-        <v>69</v>
-      </c>
-      <c r="D61" t="n">
-        <v>21.48</v>
+        <v>17.17</v>
       </c>
     </row>
   </sheetData>

--- a/files/NRL_anytime_tryscorers.xlsx
+++ b/files/NRL_anytime_tryscorers.xlsx
@@ -47,25 +47,28 @@
     <t xml:space="preserve">Kalyn Ponga</t>
   </si>
   <si>
+    <t xml:space="preserve">Francis Manuleleua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dane Gagai</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jermaine McEwen</t>
   </si>
   <si>
-    <t xml:space="preserve">Francis Manuleleua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dane Gagai</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sandon Smith</t>
   </si>
   <si>
+    <t xml:space="preserve">Thomas Cant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harrison Graham</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fletcher Hunt</t>
   </si>
   <si>
-    <t xml:space="preserve">Harrison Graham</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elijah Salesa-Leaumoana</t>
+    <t xml:space="preserve">Mat Croker</t>
   </si>
   <si>
     <t xml:space="preserve">sydney roosters</t>
@@ -98,15 +101,12 @@
     <t xml:space="preserve">Siua Wong</t>
   </si>
   <si>
+    <t xml:space="preserve">Victor Radley</t>
+  </si>
+  <si>
     <t xml:space="preserve">Reece Robson</t>
   </si>
   <si>
-    <t xml:space="preserve">Victor Radley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connor Watson</t>
-  </si>
-  <si>
     <t xml:space="preserve">Nat Butcher</t>
   </si>
   <si>
@@ -116,10 +116,10 @@
     <t xml:space="preserve">Spencer Leniu</t>
   </si>
   <si>
-    <t xml:space="preserve">Egan Butcher</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cody Ramsey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Naufahu Whyte</t>
   </si>
   <si>
     <t xml:space="preserve">Angus Crichton</t>
@@ -453,7 +453,7 @@
   <cols>
     <col min="1" max="1" width="36.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="17.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="23.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="19.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="5.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
@@ -482,7 +482,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="3">
@@ -496,7 +496,7 @@
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>2.29</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="4">
@@ -510,7 +510,7 @@
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="5">
@@ -524,7 +524,7 @@
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>3.48</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="6">
@@ -538,7 +538,7 @@
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>4.18</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="7">
@@ -566,7 +566,7 @@
         <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>4.5</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="9">
@@ -580,7 +580,7 @@
         <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>5.31</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="10">
@@ -594,7 +594,7 @@
         <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>7.38</v>
+        <v>6.12</v>
       </c>
     </row>
     <row r="11">
@@ -608,7 +608,7 @@
         <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>11.02</v>
+        <v>8.54</v>
       </c>
     </row>
     <row r="12">
@@ -622,7 +622,7 @@
         <v>16</v>
       </c>
       <c r="D12" t="n">
-        <v>12.83</v>
+        <v>10.14</v>
       </c>
     </row>
     <row r="13">
@@ -636,7 +636,7 @@
         <v>17</v>
       </c>
       <c r="D13" t="n">
-        <v>16.53</v>
+        <v>11.29</v>
       </c>
     </row>
     <row r="14">
@@ -644,13 +644,13 @@
         <v>4</v>
       </c>
       <c r="B14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" t="s">
         <v>18</v>
       </c>
-      <c r="C14" t="s">
-        <v>19</v>
-      </c>
       <c r="D14" t="n">
-        <v>1.68</v>
+        <v>19.03</v>
       </c>
     </row>
     <row r="15">
@@ -658,13 +658,13 @@
         <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C15" t="s">
         <v>20</v>
       </c>
       <c r="D15" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="16">
@@ -672,13 +672,13 @@
         <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C16" t="s">
         <v>21</v>
       </c>
       <c r="D16" t="n">
-        <v>2.36</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="17">
@@ -686,13 +686,13 @@
         <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C17" t="s">
         <v>22</v>
       </c>
       <c r="D17" t="n">
-        <v>2.79</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="18">
@@ -700,13 +700,13 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C18" t="s">
         <v>23</v>
       </c>
       <c r="D18" t="n">
-        <v>3.35</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="19">
@@ -714,13 +714,13 @@
         <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C19" t="s">
         <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>3.84</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="20">
@@ -728,13 +728,13 @@
         <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C20" t="s">
         <v>25</v>
       </c>
       <c r="D20" t="n">
-        <v>4.03</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="21">
@@ -742,13 +742,13 @@
         <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C21" t="s">
         <v>26</v>
       </c>
       <c r="D21" t="n">
-        <v>4.07</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="22">
@@ -756,13 +756,13 @@
         <v>4</v>
       </c>
       <c r="B22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C22" t="s">
         <v>27</v>
       </c>
       <c r="D22" t="n">
-        <v>4.07</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="23">
@@ -770,13 +770,13 @@
         <v>4</v>
       </c>
       <c r="B23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C23" t="s">
         <v>28</v>
       </c>
       <c r="D23" t="n">
-        <v>7.63</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="24">
@@ -784,13 +784,13 @@
         <v>4</v>
       </c>
       <c r="B24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C24" t="s">
         <v>29</v>
       </c>
       <c r="D24" t="n">
-        <v>7.91</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="25">
@@ -798,13 +798,13 @@
         <v>4</v>
       </c>
       <c r="B25" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C25" t="s">
         <v>30</v>
       </c>
       <c r="D25" t="n">
-        <v>9.18</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="26">
@@ -812,13 +812,13 @@
         <v>4</v>
       </c>
       <c r="B26" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C26" t="s">
         <v>31</v>
       </c>
       <c r="D26" t="n">
-        <v>10.19</v>
+        <v>10.41</v>
       </c>
     </row>
     <row r="27">
@@ -826,13 +826,13 @@
         <v>4</v>
       </c>
       <c r="B27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C27" t="s">
         <v>32</v>
       </c>
       <c r="D27" t="n">
-        <v>11.6</v>
+        <v>10.48</v>
       </c>
     </row>
     <row r="28">
@@ -840,13 +840,13 @@
         <v>4</v>
       </c>
       <c r="B28" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C28" t="s">
         <v>33</v>
       </c>
       <c r="D28" t="n">
-        <v>11.67</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="29">
@@ -854,13 +854,13 @@
         <v>4</v>
       </c>
       <c r="B29" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C29" t="s">
         <v>34</v>
       </c>
       <c r="D29" t="n">
-        <v>12.21</v>
+        <v>16.84</v>
       </c>
     </row>
     <row r="30">
@@ -868,13 +868,13 @@
         <v>4</v>
       </c>
       <c r="B30" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C30" t="s">
         <v>35</v>
       </c>
       <c r="D30" t="n">
-        <v>15.98</v>
+        <v>17.98</v>
       </c>
     </row>
     <row r="31">
@@ -882,13 +882,13 @@
         <v>4</v>
       </c>
       <c r="B31" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C31" t="s">
         <v>36</v>
       </c>
       <c r="D31" t="n">
-        <v>17.17</v>
+        <v>18.01</v>
       </c>
     </row>
   </sheetData>
